--- a/projects/260803_B존_8월_주차별_물량목표/260803_주차별_목표물량_산정.xlsx
+++ b/projects/260803_B존_8월_주차별_물량목표/260803_주차별_목표물량_산정.xlsx
@@ -49,7 +49,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2D5F1"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,19 +98,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -472,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M50"/>
+  <dimension ref="B1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -596,399 +605,399 @@
       <c r="M4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>8월 2주</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="8" t="n">
         <v>46237</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="8" t="n">
         <v>46243</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>1394</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="9" t="n">
+        <v>1366</v>
+      </c>
+      <c r="F5" s="10" t="n">
         <v>0.288</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>1529</v>
-      </c>
-      <c r="H5" s="6" t="n">
+      <c r="G5" s="9" t="n">
+        <v>1498</v>
+      </c>
+      <c r="H5" s="10" t="n">
         <v>0.316</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>1916</v>
-      </c>
-      <c r="J5" s="6" t="n">
+      <c r="I5" s="9" t="n">
+        <v>1878</v>
+      </c>
+      <c r="J5" s="10" t="n">
         <v>0.396</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v>4839</v>
-      </c>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
+      <c r="K5" s="9" t="n">
+        <v>4742</v>
+      </c>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>8월 3주</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="8" t="n">
         <v>46250</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>1394</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="9" t="n">
+        <v>1366</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <v>0.288</v>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>1529</v>
-      </c>
-      <c r="H6" s="6" t="n">
+      <c r="G6" s="9" t="n">
+        <v>1498</v>
+      </c>
+      <c r="H6" s="10" t="n">
         <v>0.316</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>1916</v>
-      </c>
-      <c r="J6" s="6" t="n">
+      <c r="I6" s="9" t="n">
+        <v>1878</v>
+      </c>
+      <c r="J6" s="10" t="n">
         <v>0.396</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v>4839</v>
-      </c>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
+      <c r="K6" s="9" t="n">
+        <v>4742</v>
+      </c>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>8월 4주</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="8" t="n">
         <v>46251</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="8" t="n">
         <v>46257</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>1394</v>
-      </c>
-      <c r="F7" s="6" t="n">
+      <c r="E7" s="9" t="n">
+        <v>1366</v>
+      </c>
+      <c r="F7" s="10" t="n">
         <v>0.288</v>
       </c>
-      <c r="G7" s="5" t="n">
-        <v>1529</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" s="9" t="n">
+        <v>1498</v>
+      </c>
+      <c r="H7" s="10" t="n">
         <v>0.316</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>1916</v>
-      </c>
-      <c r="J7" s="6" t="n">
+      <c r="I7" s="9" t="n">
+        <v>1878</v>
+      </c>
+      <c r="J7" s="10" t="n">
         <v>0.396</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v>4839</v>
-      </c>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
+      <c r="K7" s="9" t="n">
+        <v>4742</v>
+      </c>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>8월 5주</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="8" t="n">
         <v>46258</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="8" t="n">
         <v>46264</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>1394</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="9" t="n">
+        <v>1366</v>
+      </c>
+      <c r="F8" s="10" t="n">
         <v>0.288</v>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>1529</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="9" t="n">
+        <v>1498</v>
+      </c>
+      <c r="H8" s="10" t="n">
         <v>0.316</v>
       </c>
-      <c r="I8" s="5" t="n">
-        <v>1916</v>
-      </c>
-      <c r="J8" s="6" t="n">
+      <c r="I8" s="9" t="n">
+        <v>1878</v>
+      </c>
+      <c r="J8" s="10" t="n">
         <v>0.396</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v>4839</v>
-      </c>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
+      <c r="K8" s="9" t="n">
+        <v>4742</v>
+      </c>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>8월 소계</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="8" t="n">
-        <v>6908</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>7700</v>
-      </c>
-      <c r="H9" s="9" t="n">
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="n">
+        <v>6796</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>7576</v>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>0.318</v>
       </c>
-      <c r="I9" s="8" t="n">
-        <v>9587</v>
-      </c>
-      <c r="J9" s="9" t="n">
+      <c r="I9" s="12" t="n">
+        <v>9435</v>
+      </c>
+      <c r="J9" s="13" t="n">
         <v>0.396</v>
       </c>
-      <c r="K9" s="8" t="n">
-        <v>24195</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>18000</v>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>1.344166666666667</v>
+      <c r="K9" s="12" t="n">
+        <v>23807</v>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>21000</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>1.133666666666667</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>9월 1주</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="8" t="n">
         <v>46265</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="8" t="n">
         <v>46271</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>1311</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="E10" s="9" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>0.288</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>1439</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="G10" s="9" t="n">
+        <v>1541</v>
+      </c>
+      <c r="H10" s="10" t="n">
         <v>0.316</v>
       </c>
-      <c r="I10" s="5" t="n">
-        <v>1803</v>
-      </c>
-      <c r="J10" s="6" t="n">
+      <c r="I10" s="9" t="n">
+        <v>1931</v>
+      </c>
+      <c r="J10" s="10" t="n">
         <v>0.396</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v>4553</v>
-      </c>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
+      <c r="K10" s="9" t="n">
+        <v>4877</v>
+      </c>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>9월 2주</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="8" t="n">
         <v>46272</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="8" t="n">
         <v>46278</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="9" t="n">
+        <v>1411</v>
+      </c>
+      <c r="F11" s="10" t="n">
         <v>0.288</v>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>1424</v>
-      </c>
-      <c r="H11" s="6" t="n">
+      <c r="G11" s="9" t="n">
+        <v>1549</v>
+      </c>
+      <c r="H11" s="10" t="n">
         <v>0.316</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>1784</v>
-      </c>
-      <c r="J11" s="6" t="n">
+      <c r="I11" s="9" t="n">
+        <v>1940</v>
+      </c>
+      <c r="J11" s="10" t="n">
         <v>0.396</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v>4505</v>
-      </c>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
+      <c r="K11" s="9" t="n">
+        <v>4900</v>
+      </c>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>9월 3주</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="8" t="n">
         <v>46279</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="8" t="n">
         <v>46285</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="E12" s="9" t="n">
+        <v>1411</v>
+      </c>
+      <c r="F12" s="10" t="n">
         <v>0.288</v>
       </c>
-      <c r="G12" s="5" t="n">
-        <v>1424</v>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="G12" s="9" t="n">
+        <v>1549</v>
+      </c>
+      <c r="H12" s="10" t="n">
         <v>0.316</v>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>1784</v>
-      </c>
-      <c r="J12" s="6" t="n">
+      <c r="I12" s="9" t="n">
+        <v>1940</v>
+      </c>
+      <c r="J12" s="10" t="n">
         <v>0.396</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v>4505</v>
-      </c>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
+      <c r="K12" s="9" t="n">
+        <v>4900</v>
+      </c>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>9월 4주</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="8" t="n">
         <v>46286</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="8" t="n">
         <v>46292</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F13" s="6" t="n">
+      <c r="E13" s="9" t="n">
+        <v>1411</v>
+      </c>
+      <c r="F13" s="10" t="n">
         <v>0.288</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>1424</v>
-      </c>
-      <c r="H13" s="6" t="n">
+      <c r="G13" s="9" t="n">
+        <v>1549</v>
+      </c>
+      <c r="H13" s="10" t="n">
         <v>0.316</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>1784</v>
-      </c>
-      <c r="J13" s="6" t="n">
+      <c r="I13" s="9" t="n">
+        <v>1940</v>
+      </c>
+      <c r="J13" s="10" t="n">
         <v>0.396</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v>4505</v>
-      </c>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
+      <c r="K13" s="9" t="n">
+        <v>4900</v>
+      </c>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>9월 5주</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="8" t="n">
         <v>46293</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="8" t="n">
         <v>46295</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>556</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="9" t="n">
+        <v>605</v>
+      </c>
+      <c r="F14" s="10" t="n">
         <v>0.288</v>
       </c>
-      <c r="G14" s="5" t="n">
-        <v>610</v>
-      </c>
-      <c r="H14" s="6" t="n">
+      <c r="G14" s="9" t="n">
+        <v>664</v>
+      </c>
+      <c r="H14" s="10" t="n">
         <v>0.316</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>765</v>
-      </c>
-      <c r="J14" s="6" t="n">
+      <c r="I14" s="9" t="n">
+        <v>831</v>
+      </c>
+      <c r="J14" s="10" t="n">
         <v>0.396</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v>1931</v>
-      </c>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
+      <c r="K14" s="9" t="n">
+        <v>2100</v>
+      </c>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>9월 소계</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="8" t="n">
-        <v>5758</v>
-      </c>
-      <c r="F15" s="9" t="n">
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n">
+        <v>6243</v>
+      </c>
+      <c r="F15" s="13" t="n">
         <v>0.288</v>
       </c>
-      <c r="G15" s="8" t="n">
-        <v>6321</v>
-      </c>
-      <c r="H15" s="9" t="n">
+      <c r="G15" s="12" t="n">
+        <v>6852</v>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>0.316</v>
       </c>
-      <c r="I15" s="8" t="n">
-        <v>7920</v>
-      </c>
-      <c r="J15" s="9" t="n">
+      <c r="I15" s="12" t="n">
+        <v>8582</v>
+      </c>
+      <c r="J15" s="13" t="n">
         <v>0.396</v>
       </c>
-      <c r="K15" s="8" t="n">
-        <v>19999</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>0.99995</v>
+      <c r="K15" s="12" t="n">
+        <v>21677</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>21000</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>1.032238095238095</v>
       </c>
     </row>
     <row r="17">
@@ -1097,399 +1106,399 @@
       <c r="M20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>8월 2주</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="8" t="n">
         <v>46237</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="8" t="n">
         <v>46243</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>3004</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>0.9059999999999999</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>3316</v>
-      </c>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
+      <c r="E21" s="9" t="n">
+        <v>196</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>2266</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>0.9109999999999999</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>2488</v>
+      </c>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>8월 3주</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="8" t="n">
         <v>46250</v>
       </c>
-      <c r="E22" s="5" t="n">
-        <v>786</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>4834</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>0.843</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>5737</v>
-      </c>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
+      <c r="E22" s="9" t="n">
+        <v>467</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>3192</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>3750</v>
+      </c>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>8월 4주</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="8" t="n">
         <v>46251</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="8" t="n">
         <v>46257</v>
       </c>
-      <c r="E23" s="5" t="n">
-        <v>1547</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>6349</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>261</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>8157</v>
-      </c>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
+      <c r="E23" s="9" t="n">
+        <v>854</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>3967</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>190</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>5011</v>
+      </c>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>8월 5주</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="8" t="n">
         <v>46258</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="8" t="n">
         <v>46264</v>
       </c>
-      <c r="E24" s="5" t="n">
-        <v>2566</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>7551</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0.7140000000000001</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>461</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>10578</v>
-      </c>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
+      <c r="E24" s="9" t="n">
+        <v>1359</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>4589</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>325</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>6273</v>
+      </c>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>8월 소계</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="8" t="n">
-        <v>5290</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>23216</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>869</v>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K25" s="8" t="n">
-        <v>29375</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>0.9791666666666666</v>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n">
+        <v>2985</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>15492</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>0.8109999999999999</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>632</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>19109</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>1.005736842105263</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>9월 1주</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="8" t="n">
         <v>46265</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="8" t="n">
         <v>46271</v>
       </c>
-      <c r="E26" s="5" t="n">
-        <v>2894</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>3588</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>1085</v>
-      </c>
-      <c r="J26" s="6" t="n">
+      <c r="E26" s="9" t="n">
+        <v>2947</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>3402</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>1059</v>
+      </c>
+      <c r="J26" s="10" t="n">
         <v>0.143</v>
       </c>
-      <c r="K26" s="5" t="n">
-        <v>7567</v>
-      </c>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
+      <c r="K26" s="9" t="n">
+        <v>7408</v>
+      </c>
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>9월 2주</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="8" t="n">
         <v>46272</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="8" t="n">
         <v>46278</v>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>2834</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>2834</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="I27" s="5" t="n">
+      <c r="E27" s="9" t="n">
+        <v>3785</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>3784</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="I27" s="9" t="n">
         <v>1167</v>
       </c>
-      <c r="J27" s="6" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>6835</v>
-      </c>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
+      <c r="J27" s="10" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>8736</v>
+      </c>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>9월 3주</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="8" t="n">
         <v>46279</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="8" t="n">
         <v>46285</v>
       </c>
-      <c r="E28" s="5" t="n">
-        <v>2834</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>2834</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="I28" s="5" t="n">
+      <c r="E28" s="9" t="n">
+        <v>4462</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>4462</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>1166</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>10090</v>
+      </c>
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>9월 4주</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>46292</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>5139</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>5139</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="I29" s="9" t="n">
         <v>1167</v>
       </c>
-      <c r="J28" s="6" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>6835</v>
-      </c>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>9월 4주</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>46286</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>46292</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>2834</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>2834</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>1167</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>6835</v>
-      </c>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
+      <c r="J29" s="10" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>11445</v>
+      </c>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>9월 5주</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="8" t="n">
         <v>46293</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="8" t="n">
         <v>46295</v>
       </c>
-      <c r="E30" s="5" t="n">
-        <v>1215</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>1214</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="I30" s="5" t="n">
+      <c r="E30" s="9" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>2410</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="I30" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="J30" s="6" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>2929</v>
-      </c>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
+      <c r="J30" s="10" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>5320</v>
+      </c>
+      <c r="L30" s="7" t="n"/>
+      <c r="M30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>9월 소계</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="8" t="n">
-        <v>12611</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>13304</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>5086</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="K31" s="8" t="n">
-        <v>31001</v>
-      </c>
-      <c r="L31" s="8" t="n">
-        <v>31000</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>1.000032258064516</v>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="12" t="n">
+        <v>18743</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>19197</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>5059</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>42999</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>1.023785714285714</v>
       </c>
     </row>
     <row r="33">
@@ -1598,405 +1607,405 @@
       <c r="M36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>8월 2주</t>
         </is>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="8" t="n">
         <v>46237</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="8" t="n">
         <v>46243</v>
       </c>
-      <c r="E37" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>1345</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>919</v>
-      </c>
-      <c r="J37" s="6" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>2381</v>
-      </c>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
+      <c r="E37" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>533</v>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>1246</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>1854</v>
+      </c>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>8월 3주</t>
         </is>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="8" t="n">
         <v>46250</v>
       </c>
-      <c r="E38" s="5" t="n">
-        <v>410</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>2536</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>930</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>3876</v>
-      </c>
-      <c r="L38" s="3" t="n"/>
-      <c r="M38" s="3" t="n"/>
+      <c r="E38" s="9" t="n">
+        <v>228</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>1591</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>2611</v>
+      </c>
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>8월 4주</t>
         </is>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="8" t="n">
         <v>46251</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="8" t="n">
         <v>46257</v>
       </c>
-      <c r="E39" s="5" t="n">
-        <v>875</v>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>3555</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>940</v>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>5370</v>
-      </c>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
+      <c r="E39" s="9" t="n">
+        <v>453</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>1074</v>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="I39" s="9" t="n">
+        <v>1841</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>3368</v>
+      </c>
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>8월 5주</t>
         </is>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C40" s="8" t="n">
         <v>46258</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="8" t="n">
         <v>46264</v>
       </c>
-      <c r="E40" s="5" t="n">
-        <v>1514</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>4401</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>0.6409999999999999</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>950</v>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>6865</v>
-      </c>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
+      <c r="E40" s="9" t="n">
+        <v>749</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>1380</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>4125</v>
+      </c>
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>8월 소계</t>
         </is>
       </c>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="8" t="n">
-        <v>2924</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>12231</v>
-      </c>
-      <c r="H41" s="9" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="I41" s="8" t="n">
-        <v>4650</v>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="K41" s="8" t="n">
-        <v>19805</v>
-      </c>
-      <c r="L41" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M41" s="9" t="n">
-        <v>0.99025</v>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="12" t="n">
+        <v>1513</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>4173</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>7585</v>
+      </c>
+      <c r="J41" s="13" t="n">
+        <v>0.5720000000000001</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>13271</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>13000</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>1.020846153846154</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>9월 1주</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="8" t="n">
         <v>46265</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="8" t="n">
         <v>46271</v>
       </c>
-      <c r="E42" s="5" t="n">
-        <v>1768</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>2177</v>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>1137</v>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>5082</v>
-      </c>
-      <c r="L42" s="3" t="n"/>
-      <c r="M42" s="3" t="n"/>
+      <c r="E42" s="9" t="n">
+        <v>1735</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>1823</v>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="I42" s="9" t="n">
+        <v>1292</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>4850</v>
+      </c>
+      <c r="L42" s="7" t="n"/>
+      <c r="M42" s="7" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>9월 2주</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" s="8" t="n">
         <v>46272</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="8" t="n">
         <v>46278</v>
       </c>
-      <c r="E43" s="5" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>1738</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="I43" s="5" t="n">
+      <c r="E43" s="9" t="n">
+        <v>2309</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>2309</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>1166</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>5784</v>
+      </c>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>9월 3주</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>46285</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>2786</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>2785</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="I44" s="9" t="n">
         <v>1167</v>
       </c>
-      <c r="J43" s="6" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>4643</v>
-      </c>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="3" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>9월 3주</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>46279</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>46285</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>1738</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="I44" s="5" t="n">
+      <c r="J44" s="10" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>6738</v>
+      </c>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>9월 4주</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>46292</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>3262</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>3262</v>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="I45" s="9" t="n">
         <v>1167</v>
       </c>
-      <c r="J44" s="6" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>4643</v>
-      </c>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-    </row>
-    <row r="45">
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>9월 4주</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>46286</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>46292</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>1738</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>1738</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="I45" s="5" t="n">
-        <v>1167</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>4643</v>
-      </c>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
+      <c r="J45" s="10" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>7691</v>
+      </c>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>9월 5주</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="8" t="n">
         <v>46293</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="8" t="n">
         <v>46295</v>
       </c>
-      <c r="E46" s="5" t="n">
-        <v>745</v>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>745</v>
-      </c>
-      <c r="H46" s="6" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="I46" s="5" t="n">
+      <c r="E46" s="9" t="n">
+        <v>1544</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>1544</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I46" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="J46" s="6" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>1990</v>
-      </c>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n"/>
+      <c r="J46" s="10" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>3588</v>
+      </c>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>9월 소계</t>
         </is>
       </c>
-      <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
-      <c r="E47" s="8" t="n">
-        <v>7727</v>
-      </c>
-      <c r="F47" s="9" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="G47" s="8" t="n">
-        <v>8136</v>
-      </c>
-      <c r="H47" s="9" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="I47" s="8" t="n">
-        <v>5138</v>
-      </c>
-      <c r="J47" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="K47" s="8" t="n">
-        <v>21001</v>
-      </c>
-      <c r="L47" s="8" t="n">
-        <v>21000</v>
-      </c>
-      <c r="M47" s="9" t="n">
-        <v>1.000047619047619</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>전제: 9월 주차소계(8/31 포함) = 엑셀 월목표 → 달성률 ~100%. 성동·성북 9월 OD 각 5,000 / 잔여 50% G4·법인. 8월1주=7/27~8/2 실적.</t>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="12" t="n">
+        <v>11636</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>11723</v>
+      </c>
+      <c r="H47" s="13" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>5292</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="K47" s="12" t="n">
+        <v>28651</v>
+      </c>
+      <c r="L47" s="12" t="n">
+        <v>28000</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>1.02325</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>전제 v3: 성동·성북 리니어(합산 6.1만/4.1만→8월1.9·1.3 / 9월4.2·2.8) | 동대문 A안 합산4.2만 플랫(2.1/2.1) | 9월 OD 각5천·잔여50%G4 | 8월1주=7/27~8/2실적</t>
         </is>
       </c>
     </row>
